--- a/accountant-skill/data/output/Jan2026/inventory_summary_202601.xlsx
+++ b/accountant-skill/data/output/Jan2026/inventory_summary_202601.xlsx
@@ -80,7 +80,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="4">
+  <borders count="8">
     <border>
       <left/>
       <right/>
@@ -100,11 +100,39 @@
     <border>
       <bottom style="double"/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin"/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
@@ -133,6 +161,26 @@
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="4" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="4" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="4" fontId="6" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -504,16 +552,16 @@
   <cols>
     <col width="41" customWidth="1" min="1" max="1"/>
     <col width="24" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
     <col width="15" customWidth="1" min="6" max="6"/>
     <col width="17" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="13" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
     <col width="15" customWidth="1" min="11" max="11"/>
-    <col width="12" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -532,76 +580,83 @@
     </row>
     <row r="3"/>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
+      <c r="A4" s="4" t="inlineStr">
         <is>
           <t>RAW MATERIALS</t>
         </is>
       </c>
+      <c r="B4" s="14" t="n"/>
+      <c r="C4" s="14" t="n"/>
+      <c r="D4" s="14" t="n"/>
+      <c r="E4" s="14" t="n"/>
+      <c r="F4" s="14" t="n"/>
+      <c r="G4" s="14" t="n"/>
+      <c r="H4" s="15" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="16" t="inlineStr">
         <is>
           <t>Item Code</t>
         </is>
       </c>
-      <c r="B5" s="4" t="inlineStr">
+      <c r="B5" s="16" t="inlineStr">
         <is>
           <t>Item Name</t>
         </is>
       </c>
-      <c r="C5" s="4" t="inlineStr">
+      <c r="C5" s="16" t="inlineStr">
         <is>
           <t>Unit</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="D5" s="16" t="inlineStr">
         <is>
           <t>Opening Qty</t>
         </is>
       </c>
-      <c r="E5" s="4" t="inlineStr">
+      <c r="E5" s="16" t="inlineStr">
         <is>
           <t>Opening Value</t>
         </is>
       </c>
-      <c r="F5" s="4" t="inlineStr">
+      <c r="F5" s="16" t="inlineStr">
         <is>
           <t>Purchases Qty</t>
         </is>
       </c>
-      <c r="G5" s="4" t="inlineStr">
+      <c r="G5" s="16" t="inlineStr">
         <is>
           <t>Purchases Value</t>
         </is>
       </c>
-      <c r="H5" s="4" t="inlineStr">
+      <c r="H5" s="16" t="inlineStr">
         <is>
           <t>Issued Qty</t>
         </is>
       </c>
-      <c r="I5" s="4" t="inlineStr">
+      <c r="I5" s="16" t="inlineStr">
         <is>
           <t>Issued Value</t>
         </is>
       </c>
-      <c r="J5" s="4" t="inlineStr">
+      <c r="J5" s="16" t="inlineStr">
         <is>
           <t>Closing Qty</t>
         </is>
       </c>
-      <c r="K5" s="4" t="inlineStr">
+      <c r="K5" s="16" t="inlineStr">
         <is>
           <t>Closing Value</t>
         </is>
       </c>
-      <c r="L5" s="4" t="inlineStr">
+      <c r="L5" s="16" t="inlineStr">
         <is>
           <t>WAC</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="5" t="n">
+      <c r="A6" s="6" t="n">
         <v>12001</v>
       </c>
       <c r="B6" s="5" t="inlineStr">
@@ -609,7 +664,7 @@
           <t>Coffee Beans (Premium)</t>
         </is>
       </c>
-      <c r="C6" s="6" t="inlineStr">
+      <c r="C6" s="17" t="inlineStr">
         <is>
           <t>Bag</t>
         </is>
@@ -643,7 +698,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="5" t="n">
+      <c r="A7" s="6" t="n">
         <v>12002</v>
       </c>
       <c r="B7" s="5" t="inlineStr">
@@ -651,7 +706,7 @@
           <t>Sugar</t>
         </is>
       </c>
-      <c r="C7" s="6" t="inlineStr">
+      <c r="C7" s="17" t="inlineStr">
         <is>
           <t>Bag</t>
         </is>
@@ -685,7 +740,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="5" t="n">
+      <c r="A8" s="6" t="n">
         <v>12003</v>
       </c>
       <c r="B8" s="5" t="inlineStr">
@@ -693,7 +748,7 @@
           <t>Milk Powder</t>
         </is>
       </c>
-      <c r="C8" s="6" t="inlineStr">
+      <c r="C8" s="17" t="inlineStr">
         <is>
           <t>Bag</t>
         </is>
@@ -727,7 +782,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="5" t="n">
+      <c r="A9" s="6" t="n">
         <v>12004</v>
       </c>
       <c r="B9" s="5" t="inlineStr">
@@ -735,7 +790,7 @@
           <t>Creamer</t>
         </is>
       </c>
-      <c r="C9" s="6" t="inlineStr">
+      <c r="C9" s="17" t="inlineStr">
         <is>
           <t>Bag</t>
         </is>
@@ -769,7 +824,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="5" t="n">
+      <c r="A10" s="6" t="n">
         <v>12005</v>
       </c>
       <c r="B10" s="5" t="inlineStr">
@@ -777,7 +832,7 @@
           <t>Tea Leaves</t>
         </is>
       </c>
-      <c r="C10" s="6" t="inlineStr">
+      <c r="C10" s="17" t="inlineStr">
         <is>
           <t>Gram</t>
         </is>
@@ -811,7 +866,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="5" t="n">
+      <c r="A11" s="6" t="n">
         <v>12006</v>
       </c>
       <c r="B11" s="5" t="inlineStr">
@@ -819,7 +874,7 @@
           <t>Condensed Milk</t>
         </is>
       </c>
-      <c r="C11" s="6" t="inlineStr">
+      <c r="C11" s="17" t="inlineStr">
         <is>
           <t>Gram</t>
         </is>
@@ -853,7 +908,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="5" t="n">
+      <c r="A12" s="6" t="n">
         <v>12007</v>
       </c>
       <c r="B12" s="5" t="inlineStr">
@@ -861,7 +916,7 @@
           <t>Evaporated Milk</t>
         </is>
       </c>
-      <c r="C12" s="6" t="inlineStr">
+      <c r="C12" s="17" t="inlineStr">
         <is>
           <t>Gram</t>
         </is>
@@ -895,7 +950,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="5" t="n">
+      <c r="A13" s="6" t="n">
         <v>12008</v>
       </c>
       <c r="B13" s="5" t="inlineStr">
@@ -903,7 +958,7 @@
           <t>Flavoring Syrup</t>
         </is>
       </c>
-      <c r="C13" s="6" t="inlineStr">
+      <c r="C13" s="17" t="inlineStr">
         <is>
           <t>Bottles</t>
         </is>
@@ -937,7 +992,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="5" t="n">
+      <c r="A14" s="6" t="n">
         <v>12009</v>
       </c>
       <c r="B14" s="5" t="inlineStr">
@@ -945,7 +1000,7 @@
           <t>Chocolate Powder</t>
         </is>
       </c>
-      <c r="C14" s="6" t="inlineStr">
+      <c r="C14" s="17" t="inlineStr">
         <is>
           <t>Gram</t>
         </is>
@@ -979,7 +1034,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="5" t="n">
+      <c r="A15" s="6" t="n">
         <v>12010</v>
       </c>
       <c r="B15" s="5" t="inlineStr">
@@ -987,7 +1042,7 @@
           <t>Honey</t>
         </is>
       </c>
-      <c r="C15" s="6" t="inlineStr">
+      <c r="C15" s="17" t="inlineStr">
         <is>
           <t>Gram</t>
         </is>
@@ -1021,7 +1076,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="5" t="n">
+      <c r="A16" s="6" t="n">
         <v>12011</v>
       </c>
       <c r="B16" s="5" t="inlineStr">
@@ -1029,7 +1084,7 @@
           <t>Butter</t>
         </is>
       </c>
-      <c r="C16" s="6" t="inlineStr">
+      <c r="C16" s="17" t="inlineStr">
         <is>
           <t>Gram</t>
         </is>
@@ -1063,7 +1118,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="5" t="n">
+      <c r="A17" s="6" t="n">
         <v>12012</v>
       </c>
       <c r="B17" s="5" t="inlineStr">
@@ -1071,7 +1126,7 @@
           <t>Flour</t>
         </is>
       </c>
-      <c r="C17" s="6" t="inlineStr">
+      <c r="C17" s="17" t="inlineStr">
         <is>
           <t>Bag</t>
         </is>
@@ -1105,7 +1160,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="5" t="n">
+      <c r="A18" s="6" t="n">
         <v>12013</v>
       </c>
       <c r="B18" s="5" t="inlineStr">
@@ -1113,7 +1168,7 @@
           <t>Baking Powder</t>
         </is>
       </c>
-      <c r="C18" s="6" t="inlineStr">
+      <c r="C18" s="17" t="inlineStr">
         <is>
           <t>Gram</t>
         </is>
@@ -1147,7 +1202,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="5" t="n">
+      <c r="A19" s="6" t="n">
         <v>12014</v>
       </c>
       <c r="B19" s="5" t="inlineStr">
@@ -1155,7 +1210,7 @@
           <t>Salt</t>
         </is>
       </c>
-      <c r="C19" s="6" t="inlineStr">
+      <c r="C19" s="17" t="inlineStr">
         <is>
           <t>Gram</t>
         </is>
@@ -1189,7 +1244,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="5" t="n">
+      <c r="A20" s="6" t="n">
         <v>12015</v>
       </c>
       <c r="B20" s="5" t="inlineStr">
@@ -1197,7 +1252,7 @@
           <t>Vanilla Extract</t>
         </is>
       </c>
-      <c r="C20" s="6" t="inlineStr">
+      <c r="C20" s="17" t="inlineStr">
         <is>
           <t>Gram</t>
         </is>
@@ -1231,7 +1286,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="5" t="n">
+      <c r="A21" s="6" t="n">
         <v>12016</v>
       </c>
       <c r="B21" s="5" t="inlineStr">
@@ -1239,7 +1294,7 @@
           <t>Eggs</t>
         </is>
       </c>
-      <c r="C21" s="6" t="inlineStr">
+      <c r="C21" s="17" t="inlineStr">
         <is>
           <t>Pack</t>
         </is>
@@ -1273,7 +1328,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="5" t="n">
+      <c r="A22" s="6" t="n">
         <v>12017</v>
       </c>
       <c r="B22" s="5" t="inlineStr">
@@ -1281,7 +1336,7 @@
           <t>Oil</t>
         </is>
       </c>
-      <c r="C22" s="6" t="inlineStr">
+      <c r="C22" s="17" t="inlineStr">
         <is>
           <t>Gram</t>
         </is>
@@ -1315,7 +1370,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="5" t="n">
+      <c r="A23" s="6" t="n">
         <v>12018</v>
       </c>
       <c r="B23" s="5" t="inlineStr">
@@ -1323,7 +1378,7 @@
           <t>Other Ingredients</t>
         </is>
       </c>
-      <c r="C23" s="6" t="inlineStr">
+      <c r="C23" s="17" t="inlineStr">
         <is>
           <t>Gram</t>
         </is>
@@ -1357,103 +1412,110 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="7" t="inlineStr">
+      <c r="A24" s="18" t="inlineStr">
         <is>
           <t>Total Raw Materials</t>
         </is>
       </c>
       <c r="B24" s="8" t="inlineStr"/>
       <c r="C24" s="8" t="inlineStr"/>
-      <c r="D24" s="8" t="inlineStr"/>
-      <c r="E24" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F24" s="8" t="inlineStr"/>
-      <c r="G24" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="H24" s="8" t="inlineStr"/>
-      <c r="I24" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J24" s="8" t="inlineStr"/>
-      <c r="K24" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L24" s="8" t="inlineStr"/>
+      <c r="D24" s="10" t="inlineStr"/>
+      <c r="E24" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F24" s="10" t="inlineStr"/>
+      <c r="G24" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H24" s="10" t="inlineStr"/>
+      <c r="I24" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J24" s="10" t="inlineStr"/>
+      <c r="K24" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L24" s="10" t="inlineStr"/>
     </row>
     <row r="25"/>
     <row r="26">
-      <c r="A26" s="3" t="inlineStr">
+      <c r="A26" s="19" t="inlineStr">
         <is>
           <t>PACKAGING MATERIALS</t>
         </is>
       </c>
+      <c r="B26" s="14" t="n"/>
+      <c r="C26" s="14" t="n"/>
+      <c r="D26" s="14" t="n"/>
+      <c r="E26" s="14" t="n"/>
+      <c r="F26" s="14" t="n"/>
+      <c r="G26" s="14" t="n"/>
+      <c r="H26" s="15" t="n"/>
     </row>
     <row r="27">
-      <c r="A27" s="4" t="inlineStr">
+      <c r="A27" s="16" t="inlineStr">
         <is>
           <t>Item Code</t>
         </is>
       </c>
-      <c r="B27" s="4" t="inlineStr">
+      <c r="B27" s="16" t="inlineStr">
         <is>
           <t>Item Name</t>
         </is>
       </c>
-      <c r="C27" s="4" t="inlineStr">
+      <c r="C27" s="16" t="inlineStr">
         <is>
           <t>Unit</t>
         </is>
       </c>
-      <c r="D27" s="4" t="inlineStr">
+      <c r="D27" s="16" t="inlineStr">
         <is>
           <t>Opening Qty</t>
         </is>
       </c>
-      <c r="E27" s="4" t="inlineStr">
+      <c r="E27" s="16" t="inlineStr">
         <is>
           <t>Opening Value</t>
         </is>
       </c>
-      <c r="F27" s="4" t="inlineStr">
+      <c r="F27" s="16" t="inlineStr">
         <is>
           <t>Purchases Qty</t>
         </is>
       </c>
-      <c r="G27" s="4" t="inlineStr">
+      <c r="G27" s="16" t="inlineStr">
         <is>
           <t>Purchases Value</t>
         </is>
       </c>
-      <c r="H27" s="4" t="inlineStr">
+      <c r="H27" s="16" t="inlineStr">
         <is>
           <t>Issued Qty</t>
         </is>
       </c>
-      <c r="I27" s="4" t="inlineStr">
+      <c r="I27" s="16" t="inlineStr">
         <is>
           <t>Issued Value</t>
         </is>
       </c>
-      <c r="J27" s="4" t="inlineStr">
+      <c r="J27" s="16" t="inlineStr">
         <is>
           <t>Closing Qty</t>
         </is>
       </c>
-      <c r="K27" s="4" t="inlineStr">
+      <c r="K27" s="16" t="inlineStr">
         <is>
           <t>Closing Value</t>
         </is>
       </c>
-      <c r="L27" s="4" t="inlineStr">
+      <c r="L27" s="16" t="inlineStr">
         <is>
           <t>WAC</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="5" t="n">
+      <c r="A28" s="6" t="n">
         <v>12100</v>
       </c>
       <c r="B28" s="5" t="inlineStr">
@@ -1461,7 +1523,7 @@
           <t>Packing Bags</t>
         </is>
       </c>
-      <c r="C28" s="6" t="inlineStr">
+      <c r="C28" s="17" t="inlineStr">
         <is>
           <t>Pack</t>
         </is>
@@ -1495,7 +1557,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="5" t="n">
+      <c r="A29" s="6" t="n">
         <v>12101</v>
       </c>
       <c r="B29" s="5" t="inlineStr">
@@ -1503,7 +1565,7 @@
           <t>Small Cups</t>
         </is>
       </c>
-      <c r="C29" s="6" t="inlineStr">
+      <c r="C29" s="17" t="inlineStr">
         <is>
           <t>Pack</t>
         </is>
@@ -1537,7 +1599,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="5" t="n">
+      <c r="A30" s="6" t="n">
         <v>12102</v>
       </c>
       <c r="B30" s="5" t="inlineStr">
@@ -1545,7 +1607,7 @@
           <t>Large Cups</t>
         </is>
       </c>
-      <c r="C30" s="6" t="inlineStr">
+      <c r="C30" s="17" t="inlineStr">
         <is>
           <t>Pack</t>
         </is>
@@ -1579,7 +1641,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="5" t="n">
+      <c r="A31" s="6" t="n">
         <v>12103</v>
       </c>
       <c r="B31" s="5" t="inlineStr">
@@ -1587,7 +1649,7 @@
           <t>Lids</t>
         </is>
       </c>
-      <c r="C31" s="6" t="inlineStr">
+      <c r="C31" s="17" t="inlineStr">
         <is>
           <t>Pack</t>
         </is>
@@ -1621,7 +1683,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="5" t="n">
+      <c r="A32" s="6" t="n">
         <v>12104</v>
       </c>
       <c r="B32" s="5" t="inlineStr">
@@ -1629,7 +1691,7 @@
           <t>Straws</t>
         </is>
       </c>
-      <c r="C32" s="6" t="inlineStr">
+      <c r="C32" s="17" t="inlineStr">
         <is>
           <t>Pack</t>
         </is>
@@ -1663,7 +1725,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="5" t="n">
+      <c r="A33" s="6" t="n">
         <v>12105</v>
       </c>
       <c r="B33" s="5" t="inlineStr">
@@ -1671,7 +1733,7 @@
           <t>Napkins</t>
         </is>
       </c>
-      <c r="C33" s="6" t="inlineStr">
+      <c r="C33" s="17" t="inlineStr">
         <is>
           <t>Pack</t>
         </is>
@@ -1705,7 +1767,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="5" t="n">
+      <c r="A34" s="6" t="n">
         <v>12106</v>
       </c>
       <c r="B34" s="5" t="inlineStr">
@@ -1713,7 +1775,7 @@
           <t>Carry Bags</t>
         </is>
       </c>
-      <c r="C34" s="6" t="inlineStr">
+      <c r="C34" s="17" t="inlineStr">
         <is>
           <t>Pack</t>
         </is>
@@ -1747,40 +1809,40 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="7" t="inlineStr">
+      <c r="A35" s="18" t="inlineStr">
         <is>
           <t>Total Packaging</t>
         </is>
       </c>
       <c r="B35" s="8" t="inlineStr"/>
       <c r="C35" s="8" t="inlineStr"/>
-      <c r="D35" s="8" t="inlineStr"/>
-      <c r="E35" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F35" s="8" t="inlineStr"/>
-      <c r="G35" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="H35" s="8" t="inlineStr"/>
-      <c r="I35" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J35" s="8" t="inlineStr"/>
-      <c r="K35" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L35" s="8" t="inlineStr"/>
+      <c r="D35" s="10" t="inlineStr"/>
+      <c r="E35" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F35" s="10" t="inlineStr"/>
+      <c r="G35" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H35" s="10" t="inlineStr"/>
+      <c r="I35" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J35" s="10" t="inlineStr"/>
+      <c r="K35" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L35" s="10" t="inlineStr"/>
     </row>
     <row r="36"/>
     <row r="37">
-      <c r="A37" s="9" t="inlineStr">
+      <c r="A37" s="18" t="inlineStr">
         <is>
           <t>GRAND TOTAL</t>
         </is>
       </c>
-      <c r="B37" s="10" t="inlineStr"/>
-      <c r="C37" s="10" t="inlineStr"/>
+      <c r="B37" s="8" t="inlineStr"/>
+      <c r="C37" s="8" t="inlineStr"/>
       <c r="D37" s="10" t="inlineStr"/>
       <c r="E37" s="10" t="n">
         <v>0</v>
@@ -1802,41 +1864,58 @@
     <row r="38"/>
     <row r="39"/>
     <row r="40">
-      <c r="A40" s="3" t="inlineStr">
+      <c r="A40" s="19" t="inlineStr">
         <is>
           <t>COST OF PRODUCTION</t>
         </is>
       </c>
+      <c r="B40" s="14" t="n"/>
+      <c r="C40" s="14" t="n"/>
+      <c r="D40" s="14" t="n"/>
+      <c r="E40" s="14" t="n"/>
+      <c r="F40" s="14" t="n"/>
+      <c r="G40" s="14" t="n"/>
+      <c r="H40" s="15" t="n"/>
     </row>
     <row r="41">
-      <c r="A41" t="inlineStr">
+      <c r="A41" s="5" t="inlineStr">
         <is>
           <t>Raw Materials Used:</t>
         </is>
       </c>
-      <c r="C41" s="11" t="n">
+      <c r="C41" s="20" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="42">
-      <c r="A42" t="inlineStr">
+      <c r="A42" s="5" t="inlineStr">
         <is>
           <t>Packaging Used:</t>
         </is>
       </c>
-      <c r="C42" s="11" t="n">
+      <c r="C42" s="20" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="12" t="inlineStr">
+      <c r="A43" s="18" t="inlineStr">
         <is>
           <t>Total Cost of Materials:</t>
         </is>
       </c>
-      <c r="C43" s="13" t="n">
-        <v>0</v>
-      </c>
+      <c r="B43" s="7" t="n"/>
+      <c r="C43" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="D43" s="9" t="n"/>
+      <c r="E43" s="9" t="n"/>
+      <c r="F43" s="9" t="n"/>
+      <c r="G43" s="9" t="n"/>
+      <c r="H43" s="9" t="n"/>
+      <c r="I43" s="9" t="n"/>
+      <c r="J43" s="9" t="n"/>
+      <c r="K43" s="9" t="n"/>
+      <c r="L43" s="9" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="5">
